--- a/data/trans_dic/P19F$mañana-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19F$mañana-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la mañana</t>
+          <t>Población que, al menos, se cepilla los dientes por la mañana (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,25; 43,34</t>
+          <t>33,3; 42,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,71; 44,49</t>
+          <t>35,75; 44,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,02; 42,5</t>
+          <t>35,88; 42,42</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,93; 43,82</t>
+          <t>38,03; 43,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,3; 49,33</t>
+          <t>43,28; 49,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,3; 45,53</t>
+          <t>41,28; 45,63</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,86; 52,49</t>
+          <t>39,05; 52,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42,96; 58,11</t>
+          <t>43,6; 57,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>43,02; 52,8</t>
+          <t>42,87; 52,93</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,52; 43,17</t>
+          <t>38,79; 43,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,64; 47,44</t>
+          <t>42,59; 47,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,14; 44,6</t>
+          <t>41,3; 44,75</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se cepilla los dientes por la mañana</t>
+          <t>Población que, al menos, se cepilla los dientes por la mañana (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>130397; 169950</t>
+          <t>130577; 168448</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>190370; 237193</t>
+          <t>190561; 238815</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>333277; 393203</t>
+          <t>331940; 392482</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>429815; 496552</t>
+          <t>430990; 496653</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>434556; 495091</t>
+          <t>434363; 497505</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>882505; 972945</t>
+          <t>882063; 975005</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>96796; 127450</t>
+          <t>94831; 127588</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87556; 118444</t>
+          <t>88864; 117038</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>192156; 235816</t>
+          <t>191483; 236402</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>681204; 763323</t>
+          <t>685955; 768240</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>742122; 825762</t>
+          <t>741283; 826366</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1443369; 1564868</t>
+          <t>1449294; 1570330</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19F$mañana-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19F$mañana-Estudios-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,3; 42,96</t>
+          <t>33,54; 43,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,75; 44,8</t>
+          <t>35,98; 44,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35,88; 42,42</t>
+          <t>35,66; 42,69</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,03; 43,82</t>
+          <t>38,26; 43,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,28; 49,57</t>
+          <t>43,27; 49,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41,28; 45,63</t>
+          <t>41,42; 45,76</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,05; 52,54</t>
+          <t>39,05; 52,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>43,6; 57,42</t>
+          <t>42,86; 57,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42,87; 52,93</t>
+          <t>42,61; 52,31</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,79; 43,45</t>
+          <t>38,6; 43,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,59; 47,48</t>
+          <t>42,36; 47,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41,3; 44,75</t>
+          <t>41,24; 44,67</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>130577; 168448</t>
+          <t>131536; 169505</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>190561; 238815</t>
+          <t>191786; 235952</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>331940; 392482</t>
+          <t>329940; 394982</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>430990; 496653</t>
+          <t>433592; 498579</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>434363; 497505</t>
+          <t>434248; 496929</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>882063; 975005</t>
+          <t>885166; 977928</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>94831; 127588</t>
+          <t>94827; 127475</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88864; 117038</t>
+          <t>87355; 116764</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>191483; 236402</t>
+          <t>190332; 233649</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>685955; 768240</t>
+          <t>682509; 770376</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>741283; 826366</t>
+          <t>737361; 823575</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1449294; 1570330</t>
+          <t>1446894; 1567298</t>
         </is>
       </c>
     </row>
